--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>166</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>182</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>62</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>118</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>41</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>230</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>150</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>124</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>112</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>124</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/korea.xlsx
+++ b/output/korea.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
